--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4157C83-2777-416C-85AD-577D9308D1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEB47D9-B49D-47A8-9BE8-6089B87CD999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -215,6 +215,9 @@
   </si>
   <si>
     <t>Today is very important day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today class is impressive </t>
   </si>
 </sst>
 </file>
@@ -1086,26 +1089,50 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B8" s="14">
+        <v>400</v>
+      </c>
+      <c r="C8" s="14">
+        <v>40</v>
+      </c>
+      <c r="D8" s="14">
+        <v>180</v>
+      </c>
+      <c r="E8" s="14">
+        <v>60</v>
+      </c>
+      <c r="F8" s="14">
+        <v>150</v>
+      </c>
+      <c r="G8" s="14">
+        <v>3</v>
+      </c>
+      <c r="H8" s="14">
+        <v>350</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>260</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEB47D9-B49D-47A8-9BE8-6089B87CD999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14303B37-C227-4C5B-A224-E2B5036ABFA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -218,6 +218,9 @@
   </si>
   <si>
     <t xml:space="preserve">Today class is impressive </t>
+  </si>
+  <si>
+    <t>Lots of work today.</t>
   </si>
 </sst>
 </file>
@@ -1135,26 +1138,50 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46248</v>
+      </c>
+      <c r="B9" s="14">
+        <v>350</v>
+      </c>
+      <c r="C9" s="14">
+        <v>50</v>
+      </c>
+      <c r="D9" s="14">
+        <v>40</v>
+      </c>
+      <c r="E9" s="14">
+        <v>20</v>
+      </c>
+      <c r="F9" s="14">
+        <v>300</v>
+      </c>
+      <c r="G9" s="14">
+        <v>6</v>
+      </c>
+      <c r="H9" s="14">
+        <v>366</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1126</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>314</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14303B37-C227-4C5B-A224-E2B5036ABFA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C059CA-ADF6-4C51-87E7-C8011C2046C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t>Lots of work today.</t>
+  </si>
+  <si>
+    <t>Holiday</t>
   </si>
 </sst>
 </file>
@@ -1184,26 +1187,50 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46249</v>
+      </c>
+      <c r="B10" s="14">
+        <v>400</v>
+      </c>
+      <c r="C10" s="14">
+        <v>20</v>
+      </c>
+      <c r="D10" s="14">
+        <v>60</v>
+      </c>
+      <c r="E10" s="14">
+        <v>65</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>300</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>845</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>595</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C059CA-ADF6-4C51-87E7-C8011C2046C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC11789B-95F6-4441-8DC7-BEBA3B7FB8B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>Holiday</t>
+  </si>
+  <si>
+    <t>Feeling  good</t>
   </si>
 </sst>
 </file>
@@ -1233,26 +1236,50 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46250</v>
+      </c>
+      <c r="B11" s="14">
+        <v>420</v>
+      </c>
+      <c r="C11" s="14">
+        <v>30</v>
+      </c>
+      <c r="D11" s="14">
+        <v>60</v>
+      </c>
+      <c r="E11" s="14">
+        <v>120</v>
+      </c>
+      <c r="F11" s="14">
+        <v>350</v>
+      </c>
+      <c r="G11" s="14">
+        <v>7</v>
+      </c>
+      <c r="H11" s="14">
+        <v>250</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>210</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC11789B-95F6-4441-8DC7-BEBA3B7FB8B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A42F73-973A-414F-867D-225FC6A315A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1252,21 +1252,21 @@
         <v>120</v>
       </c>
       <c r="F11" s="14">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G11" s="14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H11" s="14">
         <v>250</v>
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>1230</v>
+        <v>880</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>210</v>
+        <v>560</v>
       </c>
       <c r="K11" s="16" t="s">
         <v>58</v>
@@ -1282,26 +1282,50 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B12" s="14">
+        <v>360</v>
+      </c>
+      <c r="C12" s="14">
+        <v>60</v>
+      </c>
+      <c r="D12" s="14">
+        <v>0</v>
+      </c>
+      <c r="E12" s="14">
+        <v>130</v>
+      </c>
+      <c r="F12" s="14">
+        <v>350</v>
+      </c>
+      <c r="G12" s="14">
+        <v>7</v>
+      </c>
+      <c r="H12" s="14">
+        <v>200</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A42F73-973A-414F-867D-225FC6A315A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955C7A1F-D73D-4AE1-84E1-C7C9B3F8D805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>Feeling  good</t>
+  </si>
+  <si>
+    <t>Full coding</t>
   </si>
 </sst>
 </file>
@@ -1328,26 +1331,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B13" s="14">
+        <v>360</v>
+      </c>
+      <c r="C13" s="14">
+        <v>60</v>
+      </c>
+      <c r="D13" s="14">
+        <v>60</v>
+      </c>
+      <c r="E13" s="14">
+        <v>180</v>
+      </c>
+      <c r="F13" s="14">
+        <v>200</v>
+      </c>
+      <c r="G13" s="14">
+        <v>4</v>
+      </c>
+      <c r="H13" s="14">
+        <v>150</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955C7A1F-D73D-4AE1-84E1-C7C9B3F8D805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DFE40CF-AED9-4FD9-B60A-125907CA831D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -230,6 +230,12 @@
   </si>
   <si>
     <t>Full coding</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Today  onlu two class</t>
   </si>
 </sst>
 </file>
@@ -1377,48 +1383,96 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B14" s="14">
+        <v>350</v>
+      </c>
+      <c r="C14" s="14">
+        <v>60</v>
+      </c>
+      <c r="D14" s="14">
+        <v>55</v>
+      </c>
+      <c r="E14" s="14">
+        <v>150</v>
+      </c>
+      <c r="F14" s="14">
+        <v>300</v>
+      </c>
+      <c r="G14" s="14">
+        <v>6</v>
+      </c>
+      <c r="H14" s="14">
+        <v>260</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1175</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>265</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B15" s="14">
+        <v>370</v>
+      </c>
+      <c r="C15" s="14">
+        <v>60</v>
+      </c>
+      <c r="D15" s="14">
+        <v>60</v>
+      </c>
+      <c r="E15" s="14">
+        <v>30</v>
+      </c>
+      <c r="F15" s="14">
+        <v>100</v>
+      </c>
+      <c r="G15" s="14">
+        <v>2</v>
+      </c>
+      <c r="H15" s="14">
+        <v>250</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DFE40CF-AED9-4FD9-B60A-125907CA831D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4FF0AA-F822-4C8F-82D7-99C7229F3E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -235,7 +235,16 @@
     <t>Unsatisfied</t>
   </si>
   <si>
-    <t>Today  onlu two class</t>
+    <t>Today  only two class</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>problem solving</t>
+  </si>
+  <si>
+    <t>Good day</t>
   </si>
 </sst>
 </file>
@@ -1475,48 +1484,96 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B16" s="14">
+        <v>350</v>
+      </c>
+      <c r="C16" s="14">
+        <v>45</v>
+      </c>
+      <c r="D16" s="14">
+        <v>30</v>
+      </c>
+      <c r="E16" s="14">
+        <v>60</v>
+      </c>
+      <c r="F16" s="14">
+        <v>250</v>
+      </c>
+      <c r="G16" s="14">
+        <v>5</v>
+      </c>
+      <c r="H16" s="14">
+        <v>250</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>985</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>455</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B17" s="14">
+        <v>360</v>
+      </c>
+      <c r="C17" s="14">
+        <v>30</v>
+      </c>
+      <c r="D17" s="14">
+        <v>40</v>
+      </c>
+      <c r="E17" s="14">
+        <v>240</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>300</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>470</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4FF0AA-F822-4C8F-82D7-99C7229F3E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC89DC79-70C9-4132-B36D-E96FF1DC47AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>Good day</t>
+  </si>
+  <si>
+    <t>Full enjoy</t>
   </si>
 </sst>
 </file>
@@ -1576,26 +1579,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B18" s="14">
+        <v>300</v>
+      </c>
+      <c r="C18" s="14">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
+        <v>60</v>
+      </c>
+      <c r="E18" s="14">
+        <v>200</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>260</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>600</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC89DC79-70C9-4132-B36D-E96FF1DC47AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99CF436-EA15-4D56-AD34-D182BBB74E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>Full enjoy</t>
+  </si>
+  <si>
+    <t>Lazy day</t>
   </si>
 </sst>
 </file>
@@ -1625,26 +1628,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B19" s="14">
+        <v>300</v>
+      </c>
+      <c r="C19" s="14">
+        <v>30</v>
+      </c>
+      <c r="D19" s="14">
+        <v>55</v>
+      </c>
+      <c r="E19" s="14">
+        <v>80</v>
+      </c>
+      <c r="F19" s="14">
+        <v>300</v>
+      </c>
+      <c r="G19" s="14">
+        <v>6</v>
+      </c>
+      <c r="H19" s="14">
+        <v>255</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99CF436-EA15-4D56-AD34-D182BBB74E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B72051-2E3A-4D70-9F03-3B65084E75EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>Lazy day</t>
+  </si>
+  <si>
+    <t>good day</t>
   </si>
 </sst>
 </file>
@@ -1674,26 +1677,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B20" s="14">
+        <v>320</v>
+      </c>
+      <c r="C20" s="14">
+        <v>40</v>
+      </c>
+      <c r="D20" s="14">
+        <v>60</v>
+      </c>
+      <c r="E20" s="14">
+        <v>50</v>
+      </c>
+      <c r="F20" s="14">
+        <v>350</v>
+      </c>
+      <c r="G20" s="14">
+        <v>7</v>
+      </c>
+      <c r="H20" s="14">
+        <v>300</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B72051-2E3A-4D70-9F03-3B65084E75EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC46A4D-B519-4883-AAC4-6039E14BED37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>good day</t>
+  </si>
+  <si>
+    <t>Nice day</t>
   </si>
 </sst>
 </file>
@@ -1723,26 +1726,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B21" s="14">
+        <v>300</v>
+      </c>
+      <c r="C21" s="14">
+        <v>60</v>
+      </c>
+      <c r="D21" s="14">
+        <v>50</v>
+      </c>
+      <c r="E21" s="14">
+        <v>80</v>
+      </c>
+      <c r="F21" s="14">
+        <v>250</v>
+      </c>
+      <c r="G21" s="14">
+        <v>5</v>
+      </c>
+      <c r="H21" s="14">
+        <v>350</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC46A4D-B519-4883-AAC4-6039E14BED37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39F5CAA-83A5-4502-8958-807734E0A153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1772,26 +1772,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B22" s="14">
+        <v>260</v>
+      </c>
+      <c r="C22" s="14">
+        <v>55</v>
+      </c>
+      <c r="D22" s="14">
+        <v>120</v>
+      </c>
+      <c r="E22" s="14">
+        <v>62</v>
+      </c>
+      <c r="F22" s="14">
+        <v>200</v>
+      </c>
+      <c r="G22" s="14">
+        <v>4</v>
+      </c>
+      <c r="H22" s="14">
+        <v>300</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>997</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>443</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39F5CAA-83A5-4502-8958-807734E0A153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D447A8-16CB-4CE0-BE54-591D93E55F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1818,26 +1818,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B23" s="14">
+        <v>300</v>
+      </c>
+      <c r="C23" s="14">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>50</v>
+      </c>
+      <c r="E23" s="14">
+        <v>90</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>260</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D447A8-16CB-4CE0-BE54-591D93E55F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA84DCA6-9A1E-4F6E-B890-B81C986A87C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,6 +257,12 @@
   </si>
   <si>
     <t>Nice day</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Nice day but lot's of work</t>
   </si>
 </sst>
 </file>
@@ -1834,21 +1840,21 @@
         <v>90</v>
       </c>
       <c r="F23" s="14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G23" s="14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H23" s="14">
         <v>260</v>
       </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>720</v>
+        <v>970</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>720</v>
+        <v>470</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>49</v>
@@ -1864,26 +1870,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B24" s="14">
+        <v>260</v>
+      </c>
+      <c r="C24" s="14">
+        <v>20</v>
+      </c>
+      <c r="D24" s="14">
+        <v>60</v>
+      </c>
+      <c r="E24" s="14">
+        <v>40</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>400</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA84DCA6-9A1E-4F6E-B890-B81C986A87C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFADA812-7D5A-4901-85F1-8C90C9FC725D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1916,26 +1916,50 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B25" s="14">
+        <v>300</v>
+      </c>
+      <c r="C25" s="14">
+        <v>35</v>
+      </c>
+      <c r="D25" s="14">
+        <v>60</v>
+      </c>
+      <c r="E25" s="14">
+        <v>90</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>250</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>735</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>705</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFADA812-7D5A-4901-85F1-8C90C9FC725D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06875890-7B32-47F7-9B45-EE0766081E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1962,26 +1962,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B26" s="14">
+        <v>320</v>
+      </c>
+      <c r="C26" s="14">
+        <v>22</v>
+      </c>
+      <c r="D26" s="14">
+        <v>90</v>
+      </c>
+      <c r="E26" s="14">
+        <v>65</v>
+      </c>
+      <c r="F26" s="14">
+        <v>300</v>
+      </c>
+      <c r="G26" s="14">
+        <v>6</v>
+      </c>
+      <c r="H26" s="14">
+        <v>200</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>997</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>443</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06875890-7B32-47F7-9B45-EE0766081E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F724D40D-9C1D-4BD1-B9BB-EEDA7A5D1357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>Nice day but lot's of work</t>
+  </si>
+  <si>
+    <t>Have to study</t>
   </si>
 </sst>
 </file>
@@ -2008,26 +2011,50 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B27" s="14">
+        <v>290</v>
+      </c>
+      <c r="C27" s="14">
+        <v>33</v>
+      </c>
+      <c r="D27" s="14">
+        <v>20</v>
+      </c>
+      <c r="E27" s="14">
+        <v>40</v>
+      </c>
+      <c r="F27" s="14">
+        <v>350</v>
+      </c>
+      <c r="G27" s="14">
+        <v>7</v>
+      </c>
+      <c r="H27" s="14">
+        <v>266</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>999</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>441</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F724D40D-9C1D-4BD1-B9BB-EEDA7A5D1357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{874843CA-181F-474D-BBE2-1ABB5767B05B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>Have to study</t>
+  </si>
+  <si>
+    <t>Ca will start</t>
   </si>
 </sst>
 </file>
@@ -2057,26 +2060,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B28" s="14">
+        <v>300</v>
+      </c>
+      <c r="C28" s="14">
+        <v>45</v>
+      </c>
+      <c r="D28" s="14">
+        <v>56</v>
+      </c>
+      <c r="E28" s="14">
+        <v>55</v>
+      </c>
+      <c r="F28" s="14">
+        <v>300</v>
+      </c>
+      <c r="G28" s="14">
+        <v>6</v>
+      </c>
+      <c r="H28" s="14">
+        <v>230</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>986</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>454</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{874843CA-181F-474D-BBE2-1ABB5767B05B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A16D842-0B02-4EFA-A3D3-6603BC4D5C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t>Ca will start</t>
+  </si>
+  <si>
+    <t>Prepare for CA</t>
   </si>
 </sst>
 </file>
@@ -2106,26 +2109,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B29" s="14">
+        <v>250</v>
+      </c>
+      <c r="C29" s="14">
+        <v>20</v>
+      </c>
+      <c r="D29" s="14">
+        <v>40</v>
+      </c>
+      <c r="E29" s="14">
+        <v>66</v>
+      </c>
+      <c r="F29" s="14">
+        <v>150</v>
+      </c>
+      <c r="G29" s="14">
+        <v>3</v>
+      </c>
+      <c r="H29" s="14">
+        <v>220</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>746</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>694</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>

--- a/12610421.xlsx
+++ b/12610421.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A16D842-0B02-4EFA-A3D3-6603BC4D5C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A932ABBC-2923-4363-8EE4-DA93156AB1EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>Prepare for CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA </t>
   </si>
 </sst>
 </file>
@@ -2155,26 +2158,50 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B30" s="14">
+        <v>300</v>
+      </c>
+      <c r="C30" s="14">
+        <v>60</v>
+      </c>
+      <c r="D30" s="14">
+        <v>66</v>
+      </c>
+      <c r="E30" s="14">
+        <v>50</v>
+      </c>
+      <c r="F30" s="14">
+        <v>200</v>
+      </c>
+      <c r="G30" s="14">
+        <v>4</v>
+      </c>
+      <c r="H30" s="14">
+        <v>312</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>988</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>452</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>
